--- a/SSC7/Grading/2 stage/6-examples/SSC7_Grading_2-stage_2026-03-12_6-examples_GPT5.5Generation_GPT5.5AutoGrading.xlsx
+++ b/SSC7/Grading/2 stage/6-examples/SSC7_Grading_2-stage_2026-03-12_6-examples_GPT5.5Generation_GPT5.5AutoGrading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/SSC7/Grading/2 stage/6-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{867B36B3-472B-3840-B550-D4A84E5732D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F112128-58B1-F44A-8F1C-1B3B674D9BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17640" yWindow="-21000" windowWidth="30240" windowHeight="17300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17640" yWindow="-21000" windowWidth="30240" windowHeight="17300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SSC7" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="155">
   <si>
     <t>Type</t>
   </si>
@@ -703,7 +703,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -832,6 +832,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7117,11 +7120,13 @@
       <c r="C53" s="28">
         <v>1</v>
       </c>
-      <c r="D53" s="48" t="s">
+      <c r="D53" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
     </row>
     <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10" t="s">
@@ -7133,8 +7138,8 @@
       <c r="C54" s="24">
         <v>1</v>
       </c>
-      <c r="D54" s="47" t="s">
-        <v>133</v>
+      <c r="D54" s="51" t="s">
+        <v>132</v>
       </c>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
